--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,33 +426,82 @@
     <t>CarePlan.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>CarePlan.extension:shallComplyWith</t>
+  </si>
+  <si>
+    <t>shallComplyWith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-shallComplyWith}
+</t>
+  </si>
+  <si>
+    <t>Resulting event shall comply with</t>
+  </si>
+  <si>
+    <t>In satisfying this request or instantiating this definition, the expectations defined in the Definition resource are expected to be met.  (This allows requirements defined elsewhere to be brought into play by reference rather than providing all of the detail in-line necessary to satisfy the referenced Definition.).</t>
+  </si>
+  <si>
+    <t>See the [notes](workflow-extensions.html#instantiation) in the workflow extensions area for more guidance on this element.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>CarePlan.extension:adheresTo</t>
+  </si>
+  <si>
+    <t>adheresTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-adheresTo}
+</t>
+  </si>
+  <si>
+    <t>Follows rules from</t>
+  </si>
+  <si>
+    <t>The action represented by this resource has been determined to satisfy the expectations established by the referenced Definition resource.</t>
+  </si>
+  <si>
+    <t>If changes are made to this event record, the determination must be made whether, with the change, the action still complies with the referenced Definition.  Revisions may result in adheresTo assertions being removed, or - if the system has an algorithm for determining which targets are appropriate - being added.  Adherence may be asserted after the fact.  It is possible for a Request or Event to adhere to a Definition even if the author/performer of the action was not aware of the Definition at the time the action was taken/requested.
+Also see the [notes](workflow-extensions.html#instantiation) in the workflow extensions area for more guidance on this element.</t>
+  </si>
+  <si>
+    <t>CarePlan.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>CarePlan.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -460,6 +509,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -513,9 +565,6 @@
     <t>Request.instantiatesCanonical</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
     <t>CarePlan.instantiatesUri</t>
   </si>
   <si>
@@ -538,7 +587,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan)
 </t>
   </si>
   <si>
@@ -826,7 +875,7 @@
     <t>CarePlan.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|Device|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|CareTeam)
 </t>
   </si>
   <si>
@@ -882,7 +931,7 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition)
 </t>
   </si>
   <si>
@@ -1002,6 +1051,9 @@
     <t>CarePlan.activity.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
@@ -1092,7 +1144,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
+    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup)
 </t>
   </si>
   <si>
@@ -1802,12 +1854,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN61"/>
+  <dimension ref="A1:AN63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.58203125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.58203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1815,7 +1867,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="163.6796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="251.53515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2771,7 +2823,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2790,17 +2842,15 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>81</v>
@@ -2837,16 +2887,14 @@
         <v>81</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2867,7 +2915,7 @@
         <v>81</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>81</v>
@@ -2881,11 +2929,13 @@
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2898,26 +2948,24 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
       </c>
@@ -2965,7 +3013,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2983,23 +3031,25 @@
         <v>81</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>81</v>
       </c>
@@ -3017,23 +3067,21 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>81</v>
       </c>
@@ -3081,7 +3129,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3093,31 +3141,31 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3130,22 +3178,26 @@
         <v>81</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3193,7 +3245,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3205,13 +3257,13 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>81</v>
@@ -3248,18 +3300,20 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3322,35 +3376,35 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
@@ -3362,18 +3416,16 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>81</v>
       </c>
@@ -3421,7 +3473,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3436,10 +3488,10 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3450,21 +3502,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
@@ -3476,20 +3528,18 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3537,7 +3587,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3552,10 +3602,10 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3566,14 +3616,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3592,18 +3642,18 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3651,7 +3701,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3666,7 +3716,7 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>81</v>
@@ -3680,45 +3730,45 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3743,13 +3793,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -3767,13 +3817,13 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
@@ -3782,16 +3832,16 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>194</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -3807,22 +3857,22 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>196</v>
@@ -3833,9 +3883,7 @@
       <c r="N18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>199</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3859,13 +3907,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3886,10 +3934,10 @@
         <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -3898,7 +3946,7 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
@@ -3912,10 +3960,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3923,34 +3971,34 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3975,13 +4023,13 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>81</v>
@@ -3999,13 +4047,13 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
@@ -4014,24 +4062,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4039,7 +4087,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>88</v>
@@ -4048,22 +4096,26 @@
         <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4087,13 +4139,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4111,10 +4163,10 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>88</v>
@@ -4126,7 +4178,7 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4140,10 +4192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4154,7 +4206,7 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -4166,17 +4218,19 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O21" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4201,13 +4255,13 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4225,13 +4279,13 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
@@ -4246,7 +4300,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4254,18 +4308,18 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4280,13 +4334,13 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4337,10 +4391,10 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>88</v>
@@ -4352,24 +4406,24 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4392,7 +4446,7 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>233</v>
@@ -4400,10 +4454,10 @@
       <c r="M23" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4451,7 +4505,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4466,32 +4520,32 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>238</v>
-      </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>88</v>
@@ -4506,20 +4560,16 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4567,10 +4617,10 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>88</v>
@@ -4582,28 +4632,28 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>252</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4622,15 +4672,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4679,7 +4731,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4694,28 +4746,28 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>81</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4734,18 +4786,20 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -4793,7 +4847,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4808,16 +4862,16 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="27">
@@ -4829,14 +4883,14 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -4845,20 +4899,18 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -4913,7 +4965,7 @@
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -4922,13 +4974,13 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>81</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>81</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4936,10 +4988,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4950,7 +5002,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -4959,21 +5011,21 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5021,13 +5073,13 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
@@ -5036,13 +5088,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5050,10 +5102,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5073,23 +5125,21 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5137,7 +5187,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5152,24 +5202,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>283</v>
+        <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5192,19 +5242,17 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5253,7 +5301,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5268,13 +5316,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5282,10 +5330,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5305,22 +5353,22 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5369,7 +5417,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5384,13 +5432,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>301</v>
@@ -5432,9 +5480,11 @@
       <c r="M32" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N32" s="2"/>
+      <c r="N32" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5495,13 +5545,13 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>307</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>308</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5512,10 +5562,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5526,7 +5576,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5538,7 +5588,7 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>214</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>311</v>
@@ -5546,8 +5596,12 @@
       <c r="M33" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="N33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5595,43 +5649,43 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5650,18 +5704,18 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>318</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>135</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5721,13 +5775,13 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>322</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5738,46 +5792,42 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -5825,25 +5875,25 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5854,14 +5904,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5880,16 +5930,16 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>326</v>
+        <v>158</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5915,13 +5965,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -5939,7 +5989,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5951,13 +6001,13 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
@@ -5968,14 +6018,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5988,25 +6038,25 @@
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>288</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>332</v>
+        <v>158</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>333</v>
+        <v>159</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6055,7 +6105,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6067,13 +6117,13 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>335</v>
+        <v>131</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
@@ -6084,10 +6134,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6110,20 +6160,18 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>337</v>
+        <v>219</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6147,13 +6195,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6171,7 +6219,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6189,21 +6237,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6214,7 +6262,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6226,7 +6274,7 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>345</v>
+        <v>303</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>346</v>
@@ -6287,25 +6335,25 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
@@ -6330,7 +6378,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6342,17 +6390,19 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6407,10 +6457,10 @@
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -6419,21 +6469,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>81</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6456,16 +6506,20 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
+        <v>361</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6513,7 +6567,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6522,16 +6576,16 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
@@ -6542,21 +6596,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6568,18 +6622,18 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>318</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>135</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6627,25 +6681,25 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -6656,46 +6710,42 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6743,25 +6793,25 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -6772,21 +6822,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -6798,18 +6848,18 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -6833,13 +6883,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>364</v>
+        <v>81</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -6857,25 +6907,25 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -6886,14 +6936,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6906,23 +6956,25 @@
         <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>157</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>370</v>
+        <v>159</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6971,7 +7023,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6983,13 +7035,13 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -7000,10 +7052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7014,7 +7066,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7026,19 +7078,17 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>162</v>
+        <v>377</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7063,13 +7113,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7087,13 +7137,13 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
@@ -7102,10 +7152,10 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>160</v>
+        <v>382</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7116,10 +7166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7130,7 +7180,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7142,19 +7192,17 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>204</v>
+        <v>384</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>173</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7179,13 +7227,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>379</v>
+        <v>81</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7203,13 +7251,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -7218,24 +7266,24 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>380</v>
+        <v>175</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>381</v>
+        <v>146</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7258,18 +7306,20 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>384</v>
+        <v>177</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N48" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7293,31 +7343,31 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7332,10 +7382,10 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>389</v>
+        <v>180</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -7346,10 +7396,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7360,7 +7410,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7372,18 +7422,20 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7407,13 +7459,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>395</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7431,13 +7483,13 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
@@ -7446,24 +7498,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>283</v>
+        <v>396</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>81</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7486,18 +7538,18 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7521,13 +7573,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7545,7 +7597,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7560,10 +7612,10 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7574,10 +7626,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7585,35 +7637,33 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>407</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7637,13 +7687,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>404</v>
+        <v>81</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -7661,13 +7711,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -7676,24 +7726,24 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>406</v>
+        <v>298</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7704,7 +7754,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -7716,18 +7766,18 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -7775,13 +7825,13 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
@@ -7790,10 +7840,10 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7804,10 +7854,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7815,7 +7865,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>88</v>
@@ -7830,7 +7880,7 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>415</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>416</v>
@@ -7847,35 +7897,33 @@
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q53" t="s" s="2">
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y53" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="R53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -7893,10 +7941,10 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>88</v>
@@ -7908,24 +7956,24 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7948,18 +7996,18 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>219</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
         <v>427</v>
       </c>
+      <c r="N54" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8007,7 +8055,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8022,24 +8070,24 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>247</v>
+        <v>429</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>428</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8056,74 +8104,76 @@
         <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q55" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="R55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8138,24 +8188,24 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8166,7 +8216,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8178,19 +8228,17 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8239,13 +8287,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -8254,10 +8302,10 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>442</v>
+        <v>262</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>443</v>
+        <v>263</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
@@ -8302,8 +8350,12 @@
       <c r="M57" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="N57" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8327,13 +8379,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8387,14 +8439,14 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8406,17 +8458,19 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8471,7 +8525,7 @@
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
@@ -8480,7 +8534,7 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>81</v>
+        <v>458</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>459</v>
@@ -8520,13 +8574,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8553,13 +8607,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>81</v>
+        <v>465</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>81</v>
+        <v>466</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -8595,25 +8649,25 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8632,16 +8686,18 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>214</v>
+        <v>471</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8689,7 +8745,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8707,21 +8763,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>343</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8732,7 +8788,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -8744,18 +8800,16 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>337</v>
+        <v>471</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
@@ -8803,13 +8857,13 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
@@ -8818,16 +8872,242 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>342</v>
+        <v>480</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>343</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
